--- a/benchmarking/materials-from-original-papers/sulfate,KSOg2=ONeill22.xlsx
+++ b/benchmarking/materials-from-original-papers/sulfate,KSOg2=ONeill22.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ehughes\projects\VolFe\benchmarking\materials-from-original-papers\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C4B0CCF-CA4E-48A0-9850-B5C5BC2E7FD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B53C582F-0ABC-48E7-A1D7-EE3D2E8CDDFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table S6 S redox calculator" sheetId="6" r:id="rId1"/>
@@ -1628,6 +1628,10 @@
       <c r="L7" s="20"/>
       <c r="M7" s="20"/>
       <c r="N7" s="20"/>
+      <c r="R7">
+        <f>LOG(C12/(1-C12))</f>
+        <v>-0.95424250943932487</v>
+      </c>
     </row>
     <row r="8" spans="1:41">
       <c r="G8" s="20"/>
@@ -1638,10 +1642,18 @@
       <c r="L8" s="20"/>
       <c r="M8" s="20"/>
       <c r="N8" s="20"/>
+      <c r="R8">
+        <f>1.36-2*U12-3.7*Y12-2.4*Z12</f>
+        <v>0.98786041270159097</v>
+      </c>
     </row>
     <row r="9" spans="1:41">
       <c r="G9" s="2" t="s">
         <v>13</v>
+      </c>
+      <c r="R9">
+        <f>4*(LOG(C12/(1-C12))+1.36-2*U12-3.7*Y12-2.4*Z12)</f>
+        <v>0.13447161304906463</v>
       </c>
     </row>
     <row r="10" spans="1:41" ht="30" customHeight="1" thickBot="1">
